--- a/residents.xlsx
+++ b/residents.xlsx
@@ -550,7 +550,7 @@
     </x:row>
     <x:row r="2" ht="23" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>עודכן: 2026-06-23</x:v>
+        <x:v>עודכן: 2026-06-26</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>

--- a/residents.xlsx
+++ b/residents.xlsx
@@ -574,7 +574,7 @@
         <x:v>פל נלי</x:v>
       </x:c>
       <x:c r="C4" s="53" t="str">
-        <x:v>‎+972523753944</x:v>
+        <x:v>‎052-375-3944</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="23" customHeight="1">
@@ -585,7 +585,7 @@
         <x:v>שוהם פרנקל (קרן שמש)</x:v>
       </x:c>
       <x:c r="C5" s="49" t="str">
-        <x:v>‎+972523815370</x:v>
+        <x:v>‎052-381-5370</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="23" customHeight="1">
@@ -596,7 +596,7 @@
         <x:v>גדי גדות</x:v>
       </x:c>
       <x:c r="C6" s="56" t="str">
-        <x:v>‎+972522846598</x:v>
+        <x:v>‎052-284-6598</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="23" customHeight="1">
@@ -607,7 +607,7 @@
         <x:v>עדי גולד</x:v>
       </x:c>
       <x:c r="C7" s="49" t="str">
-        <x:v>‎+972504314666</x:v>
+        <x:v>‎050-431-4666</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="23" customHeight="1">
@@ -618,7 +618,7 @@
         <x:v>אברמוב גבי</x:v>
       </x:c>
       <x:c r="C8" s="56" t="str">
-        <x:v>‎+972525656174</x:v>
+        <x:v>‎052-565-6174</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="23" customHeight="1">
@@ -629,7 +629,7 @@
         <x:v>הדר שיילובסקי</x:v>
       </x:c>
       <x:c r="C9" s="49" t="str">
-        <x:v>‎+972546341131</x:v>
+        <x:v>‎054-634-1131</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="23" customHeight="1">
@@ -640,7 +640,7 @@
         <x:v>מור תורג'מן</x:v>
       </x:c>
       <x:c r="C10" s="56" t="str">
-        <x:v>‎+972522254794</x:v>
+        <x:v>‎052-225-4794</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="23" customHeight="1">
@@ -651,7 +651,7 @@
         <x:v>טארק אריק</x:v>
       </x:c>
       <x:c r="C11" s="49" t="str">
-        <x:v>‎+972546651481</x:v>
+        <x:v>‎054-665-1481</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="23" customHeight="1">
@@ -662,7 +662,7 @@
         <x:v>תמר מזור (רוזנר)</x:v>
       </x:c>
       <x:c r="C12" s="56" t="str">
-        <x:v>‎+972533743023</x:v>
+        <x:v>‎053-374-3023</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="23" customHeight="1">
@@ -673,7 +673,7 @@
         <x:v>חביבה גרינברג (משה חנה)</x:v>
       </x:c>
       <x:c r="C13" s="49" t="str">
-        <x:v>‎+972503214672</x:v>
+        <x:v>‎050-321-4672</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="23" customHeight="1">
@@ -684,7 +684,7 @@
         <x:v>יבגני גרינברג</x:v>
       </x:c>
       <x:c r="C14" s="56" t="str">
-        <x:v>‎+972532465945</x:v>
+        <x:v>‎053-246-5945</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="23" customHeight="1">
@@ -695,7 +695,7 @@
         <x:v>גבאי אלכס</x:v>
       </x:c>
       <x:c r="C15" s="49" t="str">
-        <x:v>‎+972522352105</x:v>
+        <x:v>‎052-235-2105</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="23" customHeight="1">
@@ -706,7 +706,7 @@
         <x:v>אבי שיוביץ (פאולה אלמוג)</x:v>
       </x:c>
       <x:c r="C16" s="56" t="str">
-        <x:v>‎+972542228499</x:v>
+        <x:v>‎054-222-8499</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="23" customHeight="1">
@@ -717,7 +717,7 @@
         <x:v>מולהם גבאלי</x:v>
       </x:c>
       <x:c r="C17" s="49" t="str">
-        <x:v>‎+972546620031</x:v>
+        <x:v>‎054-662-0031</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="23" customHeight="1">
@@ -728,7 +728,7 @@
         <x:v>אירינה שרמן</x:v>
       </x:c>
       <x:c r="C18" s="56" t="str">
-        <x:v>‎+972502061431</x:v>
+        <x:v>‎050-206-1431</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="23" customHeight="1">
@@ -739,7 +739,7 @@
         <x:v>רונית קלמנוביץ דיקשטין</x:v>
       </x:c>
       <x:c r="C19" s="49" t="str">
-        <x:v>‎+972545954570</x:v>
+        <x:v>‎054-595-4570</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="23" customHeight="1">
@@ -750,7 +750,7 @@
         <x:v>עדן טאטור</x:v>
       </x:c>
       <x:c r="C20" s="56" t="str">
-        <x:v>‎+972546869960</x:v>
+        <x:v>‎054-686-9960</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="23" customHeight="1">
@@ -761,7 +761,7 @@
         <x:v>דן ולדסקי</x:v>
       </x:c>
       <x:c r="C21" s="49" t="str">
-        <x:v>‎+972545416261</x:v>
+        <x:v>‎054-541-6261</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="23" customHeight="1">
@@ -772,7 +772,7 @@
         <x:v>נואל רוחאנה</x:v>
       </x:c>
       <x:c r="C22" s="56" t="str">
-        <x:v>‎+972547560688</x:v>
+        <x:v>‎054-756-0688</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
@@ -783,7 +783,7 @@
         <x:v>מארון פרחאת</x:v>
       </x:c>
       <x:c r="C23" s="50" t="str">
-        <x:v>‎+972523326597</x:v>
+        <x:v>‎052-332-6597</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/residents.xlsx
+++ b/residents.xlsx
@@ -822,17 +822,17 @@
       </x:c>
       <x:c r="C18" s="0" t="inlineStr">
         <x:is>
-          <x:t>צריך לברר</x:t>
+          <x:t>מתגורר/ת</x:t>
         </x:is>
       </x:c>
       <x:c r="D18" s="0" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>Michael Ohana</x:t>
         </x:is>
       </x:c>
       <x:c r="E18" s="0" t="inlineStr">
         <x:is>
-          <x:t/>
+          <x:t>‎054-528-2774</x:t>
         </x:is>
       </x:c>
       <x:c r="F18" s="0" t="inlineStr">
@@ -852,7 +852,7 @@
       </x:c>
       <x:c r="I18" s="0" t="inlineStr">
         <x:is>
-          <x:t>לברר מי גר/ה בפועל בדירה</x:t>
+          <x:t/>
         </x:is>
       </x:c>
     </x:row>

--- a/residents.xlsx
+++ b/residents.xlsx
@@ -100,7 +100,7 @@
     <x:row r="2" ht="23" customHeight="1">
       <x:c r="A2" s="3" t="inlineStr">
         <x:is>
-          <x:t>עודכן: 2026-06-26</x:t>
+          <x:t>עודכן: 2026-07-30</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -179,12 +179,12 @@
       </x:c>
       <x:c r="F4" s="0" t="inlineStr">
         <x:is>
-          <x:t>פל נלי</x:t>
+          <x:t>פל נלי; אריאל</x:t>
         </x:is>
       </x:c>
       <x:c r="G4" s="0" t="inlineStr">
         <x:is>
-          <x:t>‎052-375-3944</x:t>
+          <x:t>נלי: ‎052-375-3944; אריאל: ‎052-436-9553</x:t>
         </x:is>
       </x:c>
       <x:c r="H4" s="0" t="inlineStr">
